--- a/outputs/577-40.xlsx
+++ b/outputs/577-40.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="17">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -64,15 +64,22 @@
     <t xml:space="preserve">1234X</t>
   </si>
   <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
     <t xml:space="preserve">datas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0_);[RED]&quot;($&quot;#,##0\)"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -98,7 +105,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,6 +116,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,7 +159,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -156,6 +169,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -411,7 +432,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="46.57"/>
@@ -455,29 +476,28 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>43741</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>123456</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="A2" s="3" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>9995</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -497,10 +517,13 @@
         <v>123456</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>868.97</v>
+        <v>9995</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -520,16 +543,10 @@
         <v>123456</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>900</v>
+        <v>868.97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -549,16 +566,16 @@
         <v>123456</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>189</v>
+        <v>300</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>425</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>80325</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -578,16 +595,10 @@
         <v>123456</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>1250</v>
+        <v>15</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -607,16 +618,16 @@
         <v>123456</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>38</v>
+        <v>425</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>4750</v>
+        <v>80325</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -636,16 +647,16 @@
         <v>123456</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>378</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -665,16 +676,16 @@
         <v>123456</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4480</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -694,16 +705,16 @@
         <v>123456</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>75</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -723,16 +734,16 @@
         <v>123456</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>1.77</v>
+        <v>32</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>143.37</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -752,16 +763,16 @@
         <v>123456</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.75</v>
+        <v>75</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>375</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>281.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -781,16 +792,16 @@
         <v>123456</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>230</v>
+        <v>1.77</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>230</v>
+        <v>143.37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -810,16 +821,16 @@
         <v>123456</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>45.45</v>
+        <v>0.75</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>409.05</v>
+        <v>281.25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -839,10 +850,16 @@
         <v>123456</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>51872.34</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -862,103 +879,97 @@
         <v>123456</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>409.05</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>1534</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>4141.8</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>43741</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>123456</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>302.08</v>
-      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>43741</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>123456</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>283.2</v>
+      <c r="A18" s="3" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>43741</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>123456</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>187.5</v>
+      <c r="A19" s="3" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -978,46 +989,36 @@
         <v>123456</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>51872.34</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>43741</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>123456</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>9995</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>9995</v>
-      </c>
+      <c r="K21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -1036,16 +1037,16 @@
         <v>123456</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>189</v>
+        <v>2.7</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>321</v>
+        <v>1534</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>60669</v>
+        <v>4141.8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1065,16 +1066,16 @@
         <v>123456</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>189</v>
+        <v>37.76</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>241</v>
+        <v>8</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>45549</v>
+        <v>302.08</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,16 +1095,16 @@
         <v>123456</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>125</v>
+        <v>35.4</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1500</v>
+        <v>283.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1123,16 +1124,16 @@
         <v>123456</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>125</v>
+        <v>62.5</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>5750</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1152,16 +1153,16 @@
         <v>123456</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1890</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1181,16 +1182,16 @@
         <v>123456</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>189</v>
+        <v>9995</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>378</v>
+        <v>9995</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1210,16 +1211,16 @@
         <v>123456</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>5888</v>
+        <v>60669</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1239,16 +1240,16 @@
         <v>123456</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.3</v>
+        <v>189</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>700</v>
+        <v>241</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>210</v>
+        <v>45549</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1268,16 +1269,16 @@
         <v>123456</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>1.77</v>
+        <v>125</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>670</v>
+        <v>12</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1185.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1297,16 +1298,16 @@
         <v>123456</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>230</v>
+        <v>125</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>1035</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1326,16 +1327,16 @@
         <v>123456</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>3734.29</v>
+        <v>189</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>3743.29</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1355,16 +1356,16 @@
         <v>123456</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>1785</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1384,16 +1385,16 @@
         <v>123456</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>37.76</v>
+        <v>32</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>566.4</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1413,16 +1414,16 @@
         <v>123456</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>35</v>
+        <v>700</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>630</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1442,16 +1443,16 @@
         <v>123456</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>18</v>
+        <v>1.77</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>2</v>
+        <v>670</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>36</v>
+        <v>1185.9</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1471,16 +1472,16 @@
         <v>123456</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>35.4</v>
+        <v>230</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>247.8</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1500,16 +1501,16 @@
         <v>123456</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>45.45</v>
+        <v>3734.29</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>4317.75</v>
+        <v>3743.29</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1529,16 +1530,16 @@
         <v>123456</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>288.25</v>
+        <v>85</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>288.25</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1558,16 +1559,16 @@
         <v>123456</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>1952.25</v>
+        <v>37.76</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1952.25</v>
+        <v>566.4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1587,16 +1588,16 @@
         <v>123456</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>1857</v>
+        <v>18</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>1857</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,16 +1617,16 @@
         <v>123456</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>62.5</v>
+        <v>18</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1645,16 +1646,16 @@
         <v>123456</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>75</v>
+        <v>35.4</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>600</v>
+        <v>247.8</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1674,10 +1675,16 @@
         <v>123456</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>95</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>59583.03</v>
+        <v>4317.75</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1697,15 +1704,212 @@
         <v>123456</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I45" s="1" t="n">
+        <v>288.25</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>288.25</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>123456</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>1952.25</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>1952.25</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>123456</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>1857</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>123456</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>123456</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>123456</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>59583.03</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>43741</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>123456</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="1" t="n">
         <v>2.7</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J52" s="1" t="n">
         <v>4375</v>
       </c>
-      <c r="K45" s="1" t="n">
+      <c r="K52" s="1" t="n">
         <v>11812.5</v>
       </c>
     </row>
